--- a/Realistic_ER_Estimate/NTu/aggregate_Kabianga_results.xlsx
+++ b/Realistic_ER_Estimate/NTu/aggregate_Kabianga_results.xlsx
@@ -425,342 +425,854 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tea</t>
+          <t>Tea - SOC Baseline (tCO2e/ha)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Napier</t>
+          <t>Tea - SOC Project (tCO2e/ha)</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Tea - ERs (tCO2e/ha)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Napier - SOC Baseline (tCO2e/ha)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Napier - SOC Project (tCO2e/ha)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Napier - ERs (tCO2e/ha)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
+      <c r="A2" t="n">
+        <v>416.7166577479397</v>
+      </c>
+      <c r="B2" t="n">
+        <v>416.7161654532999</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>416.7233234960866</v>
+      </c>
+      <c r="E2" t="n">
+        <v>416.7222264445465</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>368.6575560495097</v>
+      </c>
+      <c r="B3" t="n">
+        <v>416.7161622645597</v>
+      </c>
+      <c r="C3" t="n">
         <v>48.05909850968993</v>
       </c>
-      <c r="B3" t="n">
+      <c r="D3" t="n">
+        <v>378.2922970603245</v>
+      </c>
+      <c r="E3" t="n">
+        <v>416.7222232828124</v>
+      </c>
+      <c r="F3" t="n">
         <v>38.4310232740281</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>343.435553356468</v>
+      </c>
+      <c r="B4" t="n">
+        <v>416.7161593602667</v>
+      </c>
+      <c r="C4" t="n">
         <v>25.22199978874856</v>
       </c>
-      <c r="B4" t="n">
+      <c r="D4" t="n">
+        <v>358.1473009650054</v>
+      </c>
+      <c r="E4" t="n">
+        <v>416.7222204032941</v>
+      </c>
+      <c r="F4" t="n">
         <v>20.14499321580071</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
+        <v>327.6465635798917</v>
+      </c>
+      <c r="B5" t="n">
+        <v>416.7161567150468</v>
+      </c>
+      <c r="C5" t="n">
         <v>15.78898713135645</v>
       </c>
-      <c r="B5" t="n">
+      <c r="D5" t="n">
+        <v>345.5740716431207</v>
+      </c>
+      <c r="E5" t="n">
+        <v>416.7222177808016</v>
+      </c>
+      <c r="F5" t="n">
         <v>12.5732266993922</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>316.9182202909282</v>
+      </c>
+      <c r="B6" t="n">
+        <v>416.71615430579</v>
+      </c>
+      <c r="C6" t="n">
         <v>10.72834087970669</v>
       </c>
-      <c r="B6" t="n">
+      <c r="D6" t="n">
+        <v>337.076204601673</v>
+      </c>
+      <c r="E6" t="n">
+        <v>416.7222153923926</v>
+      </c>
+      <c r="F6" t="n">
         <v>8.497864653038652</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
+        <v>308.9840885953359</v>
+      </c>
+      <c r="B7" t="n">
+        <v>416.7161521114476</v>
+      </c>
+      <c r="C7" t="n">
         <v>7.934129501249832</v>
       </c>
-      <c r="B7" t="n">
+      <c r="D7" t="n">
+        <v>330.8390734480881</v>
+      </c>
+      <c r="E7" t="n">
+        <v>416.7222132171726</v>
+      </c>
+      <c r="F7" t="n">
         <v>6.23712897836504</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
+        <v>302.6542640667927</v>
+      </c>
+      <c r="B8" t="n">
+        <v>416.7161501128483</v>
+      </c>
+      <c r="C8" t="n">
         <v>6.329822529943949</v>
       </c>
-      <c r="B8" t="n">
+      <c r="D8" t="n">
+        <v>325.9081120296966</v>
+      </c>
+      <c r="E8" t="n">
+        <v>416.7222112361128</v>
+      </c>
+      <c r="F8" t="n">
         <v>4.930959437331623</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
+        <v>297.2969900990153</v>
+      </c>
+      <c r="B9" t="n">
+        <v>416.7161482925313</v>
+      </c>
+      <c r="C9" t="n">
         <v>5.357272147460449</v>
       </c>
-      <c r="B9" t="n">
+      <c r="D9" t="n">
+        <v>321.7749716032007</v>
+      </c>
+      <c r="E9" t="n">
+        <v>416.722209431882</v>
+      </c>
+      <c r="F9" t="n">
         <v>4.133138622265122</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
+        <v>292.572426127807</v>
+      </c>
+      <c r="B10" t="n">
+        <v>416.716146634593</v>
+      </c>
+      <c r="C10" t="n">
         <v>4.724562313269995</v>
       </c>
-      <c r="B10" t="n">
+      <c r="D10" t="n">
+        <v>318.164908912187</v>
+      </c>
+      <c r="E10" t="n">
+        <v>416.7222077886968</v>
+      </c>
+      <c r="F10" t="n">
         <v>3.610061047828486</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
+        <v>288.2943173190648</v>
+      </c>
+      <c r="B11" t="n">
+        <v>416.7161451245489</v>
+      </c>
+      <c r="C11" t="n">
         <v>4.278107298698013</v>
       </c>
-      <c r="B11" t="n">
+      <c r="D11" t="n">
+        <v>314.9262627654611</v>
+      </c>
+      <c r="E11" t="n">
+        <v>416.7222062921819</v>
+      </c>
+      <c r="F11" t="n">
         <v>3.238644650211024</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
+        <v>284.3576283942813</v>
+      </c>
+      <c r="B12" t="n">
+        <v>416.7161437492061</v>
+      </c>
+      <c r="C12" t="n">
         <v>3.93668754944071</v>
       </c>
-      <c r="B12" t="n">
+      <c r="D12" t="n">
+        <v>311.9725991631096</v>
+      </c>
+      <c r="E12" t="n">
+        <v>416.7222049292458</v>
+      </c>
+      <c r="F12" t="n">
         <v>2.953662239415342</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
+        <v>280.700528964624</v>
+      </c>
+      <c r="B13" t="n">
+        <v>416.7161424965486</v>
+      </c>
+      <c r="C13" t="n">
         <v>3.657098176999961</v>
       </c>
-      <c r="B13" t="n">
+      <c r="D13" t="n">
+        <v>309.2522959892933</v>
+      </c>
+      <c r="E13" t="n">
+        <v>416.7222036879653</v>
+      </c>
+      <c r="F13" t="n">
         <v>2.720301932535866</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
+        <v>277.284367858171</v>
+      </c>
+      <c r="B14" t="n">
+        <v>416.7161413556326</v>
+      </c>
+      <c r="C14" t="n">
         <v>3.416159965536887</v>
       </c>
-      <c r="B14" t="n">
+      <c r="D14" t="n">
+        <v>306.7325043350234</v>
+      </c>
+      <c r="E14" t="n">
+        <v>416.7222025574815</v>
+      </c>
+      <c r="F14" t="n">
         <v>2.519790523786028</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
+        <v>274.083098497751</v>
+      </c>
+      <c r="B15" t="n">
+        <v>416.7161403164905</v>
+      </c>
+      <c r="C15" t="n">
         <v>3.201268321277941</v>
       </c>
-      <c r="B15" t="n">
+      <c r="D15" t="n">
+        <v>304.3906672851459</v>
+      </c>
+      <c r="E15" t="n">
+        <v>416.7222015279044</v>
+      </c>
+      <c r="F15" t="n">
         <v>2.341836020300514</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
+        <v>271.0776795649007</v>
+      </c>
+      <c r="B16" t="n">
+        <v>416.7161393700435</v>
+      </c>
+      <c r="C16" t="n">
         <v>3.00541798640325</v>
       </c>
-      <c r="B16" t="n">
+      <c r="D16" t="n">
+        <v>302.2100197158653</v>
+      </c>
+      <c r="E16" t="n">
+        <v>416.7222005902274</v>
+      </c>
+      <c r="F16" t="n">
         <v>2.18064663160357</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
+        <v>268.2530983994151</v>
+      </c>
+      <c r="B17" t="n">
+        <v>416.7161385080228</v>
+      </c>
+      <c r="C17" t="n">
         <v>2.824580303464799</v>
       </c>
-      <c r="B17" t="n">
+      <c r="D17" t="n">
+        <v>300.1771882958594</v>
+      </c>
+      <c r="E17" t="n">
+        <v>416.7221997362474</v>
+      </c>
+      <c r="F17" t="n">
         <v>2.03283056602586</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
+        <v>265.5967786350491</v>
+      </c>
+      <c r="B18" t="n">
+        <v>416.7161377228974</v>
+      </c>
+      <c r="C18" t="n">
         <v>2.656318979240751</v>
       </c>
-      <c r="B18" t="n">
+      <c r="D18" t="n">
+        <v>298.2809010145053</v>
+      </c>
+      <c r="E18" t="n">
+        <v>416.7221989584937</v>
+      </c>
+      <c r="F18" t="n">
         <v>1.89628650360037</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
+        <v>263.0977194130962</v>
+      </c>
+      <c r="B19" t="n">
+        <v>416.7161370078083</v>
+      </c>
+      <c r="C19" t="n">
         <v>2.499058506863757</v>
       </c>
-      <c r="B19" t="n">
+      <c r="D19" t="n">
+        <v>296.511283880295</v>
+      </c>
+      <c r="E19" t="n">
+        <v>416.7221982501621</v>
+      </c>
+      <c r="F19" t="n">
         <v>1.769616425878667</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
+        <v>260.7460219909864</v>
+      </c>
+      <c r="B20" t="n">
+        <v>416.7161363565076</v>
+      </c>
+      <c r="C20" t="n">
         <v>2.351696770809122</v>
       </c>
-      <c r="B20" t="n">
+      <c r="D20" t="n">
+        <v>294.8594691501232</v>
+      </c>
+      <c r="E20" t="n">
+        <v>416.722197605056</v>
+      </c>
+      <c r="F20" t="n">
         <v>1.651814085065785</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
+        <v>258.5326221213709</v>
+      </c>
+      <c r="B21" t="n">
+        <v>416.7161357633055</v>
+      </c>
+      <c r="C21" t="n">
         <v>2.213399276413384</v>
       </c>
-      <c r="B21" t="n">
+      <c r="D21" t="n">
+        <v>293.317369529609</v>
+      </c>
+      <c r="E21" t="n">
+        <v>416.7221970175321</v>
+      </c>
+      <c r="F21" t="n">
         <v>1.542099032990204</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
+        <v>256.4491322870616</v>
+      </c>
+      <c r="B22" t="n">
+        <v>416.7161352230189</v>
+      </c>
+      <c r="C22" t="n">
         <v>2.083489294022693</v>
       </c>
-      <c r="B22" t="n">
+      <c r="D22" t="n">
+        <v>291.8775414054151</v>
+      </c>
+      <c r="E22" t="n">
+        <v>416.7221964824505</v>
+      </c>
+      <c r="F22" t="n">
         <v>1.439827589112402</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
+        <v>254.4877430870559</v>
+      </c>
+      <c r="B23" t="n">
+        <v>416.7161347309275</v>
+      </c>
+      <c r="C23" t="n">
         <v>1.961388707914362</v>
       </c>
-      <c r="B23" t="n">
+      <c r="D23" t="n">
+        <v>290.5330963859873</v>
+      </c>
+      <c r="E23" t="n">
+        <v>416.7221959951303</v>
+      </c>
+      <c r="F23" t="n">
         <v>1.344444532107507</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
+        <v>252.6411569252942</v>
+      </c>
+      <c r="B24" t="n">
+        <v>416.7161342827328</v>
+      </c>
+      <c r="C24" t="n">
         <v>1.846585713566929</v>
       </c>
-      <c r="B24" t="n">
+      <c r="D24" t="n">
+        <v>289.2776395487439</v>
+      </c>
+      <c r="E24" t="n">
+        <v>416.7221955513084</v>
+      </c>
+      <c r="F24" t="n">
         <v>1.255456393421587</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
+        <v>250.9025397481395</v>
+      </c>
+      <c r="B25" t="n">
+        <v>416.7161338745187</v>
+      </c>
+      <c r="C25" t="n">
         <v>1.738616768940631</v>
       </c>
-      <c r="B25" t="n">
+      <c r="D25" t="n">
+        <v>288.1052228934184</v>
+      </c>
+      <c r="E25" t="n">
+        <v>416.722195147102</v>
+      </c>
+      <c r="F25" t="n">
         <v>1.172416251119046</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
+        <v>249.2654832295433</v>
+      </c>
+      <c r="B26" t="n">
+        <v>416.7161335027185</v>
+      </c>
+      <c r="C26" t="n">
         <v>1.637056146796032</v>
       </c>
-      <c r="B26" t="n">
+      <c r="D26" t="n">
+        <v>287.0103078420606</v>
+      </c>
+      <c r="E26" t="n">
+        <v>416.7221947789749</v>
+      </c>
+      <c r="F26" t="n">
         <v>1.094914683230774</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
+        <v>247.7239733206067</v>
+      </c>
+      <c r="B27" t="n">
+        <v>416.7161331640843</v>
+      </c>
+      <c r="C27" t="n">
         <v>1.541509570302405</v>
       </c>
-      <c r="B27" t="n">
+      <c r="D27" t="n">
+        <v>285.9877334534025</v>
+      </c>
+      <c r="E27" t="n">
+        <v>416.7221944437069</v>
+      </c>
+      <c r="F27" t="n">
         <v>1.022574053390031</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
+        <v>246.2723629430459</v>
+      </c>
+      <c r="B28" t="n">
+        <v>416.7161328556575</v>
+      </c>
+      <c r="C28" t="n">
         <v>1.45161006913393</v>
       </c>
-      <c r="B28" t="n">
+      <c r="D28" t="n">
+        <v>285.0326885189349</v>
+      </c>
+      <c r="E28" t="n">
+        <v>416.7221941383646</v>
+      </c>
+      <c r="F28" t="n">
         <v>0.9550446291253678</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
+        <v>244.9053475949379</v>
+      </c>
+      <c r="B29" t="n">
+        <v>416.7161325747434</v>
+      </c>
+      <c r="C29" t="n">
         <v>1.367015067193909</v>
       </c>
-      <c r="B29" t="n">
+      <c r="D29" t="n">
+        <v>284.1406865061445</v>
+      </c>
+      <c r="E29" t="n">
+        <v>416.7221938602773</v>
+      </c>
+      <c r="F29" t="n">
         <v>0.8920017347030722</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
+        <v>243.6179431642113</v>
+      </c>
+      <c r="B30" t="n">
+        <v>416.7161323188877</v>
+      </c>
+      <c r="C30" t="n">
         <v>1.287404174870934</v>
       </c>
-      <c r="B30" t="n">
+      <c r="D30" t="n">
+        <v>283.3075427414952</v>
+      </c>
+      <c r="E30" t="n">
+        <v>416.7221936070121</v>
+      </c>
+      <c r="F30" t="n">
         <v>0.833143511384184</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
+        <v>242.4054655282098</v>
+      </c>
+      <c r="B31" t="n">
+        <v>416.7161320858555</v>
+      </c>
+      <c r="C31" t="n">
         <v>1.212477402969251</v>
       </c>
-      <c r="B31" t="n">
+      <c r="D31" t="n">
+        <v>282.5293534564421</v>
+      </c>
+      <c r="E31" t="n">
+        <v>416.7221933763533</v>
+      </c>
+      <c r="F31" t="n">
         <v>0.7781890543942845</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
+        <v>241.2635116711683</v>
+      </c>
+      <c r="B32" t="n">
+        <v>416.7161318736105</v>
+      </c>
+      <c r="C32" t="n">
         <v>1.141953644796568</v>
       </c>
-      <c r="B32" t="n">
+      <c r="D32" t="n">
+        <v>281.802476446265</v>
+      </c>
+      <c r="E32" t="n">
+        <v>416.722193166283</v>
+      </c>
+      <c r="F32" t="n">
         <v>0.7268768001068224</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
+        <v>240.1879421362585</v>
+      </c>
+      <c r="B33" t="n">
+        <v>416.7161316802985</v>
+      </c>
+      <c r="C33" t="n">
         <v>1.075569341597732</v>
       </c>
-      <c r="B33" t="n">
+      <c r="D33" t="n">
+        <v>281.12351316254</v>
+      </c>
+      <c r="E33" t="n">
+        <v>416.7221929749637</v>
+      </c>
+      <c r="F33" t="n">
         <v>0.678963092405624</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
+        <v>239.1748646770669</v>
+      </c>
+      <c r="B34" t="n">
+        <v>416.7161315042308</v>
+      </c>
+      <c r="C34" t="n">
         <v>1.013077283123782</v>
       </c>
-      <c r="B34" t="n">
+      <c r="D34" t="n">
+        <v>280.4892921014239</v>
+      </c>
+      <c r="E34" t="n">
+        <v>416.7221928007214</v>
+      </c>
+      <c r="F34" t="n">
         <v>0.6342208868738576</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
+        <v>238.2206190019269</v>
+      </c>
+      <c r="B35" t="n">
+        <v>416.7161313438687</v>
+      </c>
+      <c r="C35" t="n">
         <v>0.9542455147779947</v>
       </c>
-      <c r="B35" t="n">
+      <c r="D35" t="n">
+        <v>279.8968533752493</v>
+      </c>
+      <c r="E35" t="n">
+        <v>416.7221926420322</v>
+      </c>
+      <c r="F35" t="n">
         <v>0.5924385674853406</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
+        <v>237.321762522414</v>
+      </c>
+      <c r="B36" t="n">
+        <v>416.7161311978115</v>
+      </c>
+      <c r="C36" t="n">
         <v>0.8988563334557398</v>
       </c>
-      <c r="B36" t="n">
+      <c r="D36" t="n">
+        <v>279.3434343714741</v>
+      </c>
+      <c r="E36" t="n">
+        <v>416.7221924975073</v>
+      </c>
+      <c r="F36" t="n">
         <v>0.5534188592502716</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
+        <v>236.4750570293285</v>
+      </c>
+      <c r="B37" t="n">
+        <v>416.7161310647832</v>
+      </c>
+      <c r="C37" t="n">
         <v>0.8467053600572333</v>
       </c>
-      <c r="B37" t="n">
+      <c r="D37" t="n">
+        <v>278.8264564146648</v>
+      </c>
+      <c r="E37" t="n">
+        <v>416.7221923658828</v>
+      </c>
+      <c r="F37" t="n">
         <v>0.5169778251847532</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
+        <v>235.6774562281564</v>
+      </c>
+      <c r="B38" t="n">
+        <v>416.7161309436214</v>
+      </c>
+      <c r="C38" t="n">
         <v>0.797600680010324</v>
       </c>
-      <c r="B38" t="n">
+      <c r="D38" t="n">
+        <v>278.3435123559629</v>
+      </c>
+      <c r="E38" t="n">
+        <v>416.722192246007</v>
+      </c>
+      <c r="F38" t="n">
         <v>0.4829439388261487</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
+        <v>234.9260940727048</v>
+      </c>
+      <c r="B39" t="n">
+        <v>416.716130833268</v>
+      </c>
+      <c r="C39" t="n">
         <v>0.7513620450981051</v>
       </c>
-      <c r="B39" t="n">
+      <c r="D39" t="n">
+        <v>277.8923550215324</v>
+      </c>
+      <c r="E39" t="n">
+        <v>416.7221921368312</v>
+      </c>
+      <c r="F39" t="n">
         <v>0.4511572252546851</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
+        <v>234.2182738410848</v>
+      </c>
+      <c r="B40" t="n">
+        <v>416.7161307327582</v>
+      </c>
+      <c r="C40" t="n">
         <v>0.7078201311102935</v>
       </c>
-      <c r="B40" t="n">
+      <c r="D40" t="n">
+        <v>277.4708864574041</v>
+      </c>
+      <c r="E40" t="n">
+        <v>416.7221920374006</v>
+      </c>
+      <c r="F40" t="n">
         <v>0.4214684646976868</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
+        <v>233.551457902875</v>
+      </c>
+      <c r="B41" t="n">
+        <v>416.7161306412145</v>
+      </c>
+      <c r="C41" t="n">
         <v>0.666815846666052</v>
       </c>
-      <c r="B41" t="n">
+      <c r="D41" t="n">
+        <v>277.0771479132698</v>
+      </c>
+      <c r="E41" t="n">
+        <v>416.7221919468452</v>
+      </c>
+      <c r="F41" t="n">
         <v>0.3937384535788955</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
+        <v>232.923258130383</v>
+      </c>
+      <c r="B42" t="n">
+        <v>416.7161305578367</v>
+      </c>
+      <c r="C42" t="n">
         <v>0.6281996891142233</v>
       </c>
-      <c r="B42" t="n">
+      <c r="D42" t="n">
+        <v>276.7093105123463</v>
+      </c>
+      <c r="E42" t="n">
+        <v>416.7221918643729</v>
+      </c>
+      <c r="F42" t="n">
         <v>0.3678373184511656</v>
       </c>
     </row>
